--- a/data/trans_orig/IP1002-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1002-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>447</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>8419</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101548</t>
+          <t>101558</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105726</t>
+          <t>105724</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114798</t>
+          <t>114988</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120724</t>
+          <t>120723</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>218975</t>
+          <t>219132</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>225707</t>
+          <t>225768</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>866</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12720</t>
+          <t>12739</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>244825</t>
+          <t>244846</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>251780</t>
+          <t>251449</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>246010</t>
+          <t>246297</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>252884</t>
+          <t>252890</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>494241</t>
+          <t>494222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>503269</t>
+          <t>503523</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7234</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120495</t>
+          <t>120314</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126298</t>
+          <t>126381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137397</t>
+          <t>137476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>260955</t>
+          <t>260067</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>267655</t>
+          <t>267623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>190579</t>
+          <t>190591</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>200634</t>
+          <t>200115</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>205385</t>
+          <t>205382</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>394078</t>
+          <t>393515</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13975</t>
+          <t>14763</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>12396</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27440</t>
+          <t>25768</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>666028</t>
+          <t>665636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>676066</t>
+          <t>675450</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>708725</t>
+          <t>707937</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>718307</t>
+          <t>717875</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1376281</t>
+          <t>1377953</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1391723</t>
+          <t>1391325</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8783</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>14597</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>136858</t>
+          <t>136831</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144330</t>
+          <t>143915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135730</t>
+          <t>135760</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>142561</t>
+          <t>143102</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276185</t>
+          <t>276197</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>285809</t>
+          <t>286165</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15562</t>
+          <t>15352</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20390</t>
+          <t>20763</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>226338</t>
+          <t>225592</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>233069</t>
+          <t>233057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>251539</t>
+          <t>251749</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>261921</t>
+          <t>262043</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>481186</t>
+          <t>480813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>493447</t>
+          <t>493495</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149797</t>
+          <t>149766</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151539</t>
+          <t>151234</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157270</t>
+          <t>157274</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>303197</t>
+          <t>304372</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>311359</t>
+          <t>311412</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167988</t>
+          <t>167297</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173130</t>
+          <t>172985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343402</t>
+          <t>344033</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17024</t>
+          <t>17518</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27606</t>
+          <t>26197</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>20506</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>37721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>689904</t>
+          <t>689410</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>700970</t>
+          <t>700506</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>720536</t>
+          <t>721945</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>735507</t>
+          <t>736536</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1416315</t>
+          <t>1417349</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1433952</t>
+          <t>1434564</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>450</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11683</t>
+          <t>11883</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>127355</t>
+          <t>127362</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131195</t>
+          <t>131204</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113844</t>
+          <t>114713</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121575</t>
+          <t>121605</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>244135</t>
+          <t>243935</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>252395</t>
+          <t>252158</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5996</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13645</t>
+          <t>14046</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>200358</t>
+          <t>200535</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>207911</t>
+          <t>208511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>252065</t>
+          <t>251525</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>257380</t>
+          <t>257421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>454933</t>
+          <t>454532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>464274</t>
+          <t>464177</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>183927</t>
+          <t>183800</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>372449</t>
+          <t>372508</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>168846</t>
+          <t>169388</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>169482</t>
+          <t>169841</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341990</t>
+          <t>342698</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>13589</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16412</t>
+          <t>16307</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,47 +6049,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>17791</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>11636</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>25341</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>17791</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>12131</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>25866</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>691713</t>
+          <t>690782</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>700379</t>
+          <t>700220</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>728432</t>
+          <t>728537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>738887</t>
+          <t>738753</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,47 +6162,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1431424</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1423874</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1437579</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>99,2%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2099</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1431424</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1423349</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1437084</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53284</t>
+          <t>53217</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114565</t>
+          <t>114413</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>9279</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>11413</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16699</t>
+          <t>17541</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>150074</t>
+          <t>150020</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>157411</t>
+          <t>157402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>170656</t>
+          <t>171141</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>180742</t>
+          <t>180750</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>325154</t>
+          <t>324312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>336852</t>
+          <t>336701</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>165481</t>
+          <t>165655</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>172266</t>
+          <t>172286</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>206383</t>
+          <t>206401</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>375248</t>
+          <t>374951</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>382948</t>
+          <t>382914</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>850</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>10508</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>879</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11285</t>
+          <t>10193</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>293960</t>
+          <t>294975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>304586</t>
+          <t>304633</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>569655</t>
+          <t>570747</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>579603</t>
+          <t>580061</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>15481</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18656</t>
+          <t>19366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28318</t>
+          <t>29264</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>650470</t>
+          <t>649859</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>660691</t>
+          <t>660303</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>742313</t>
+          <t>741603</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>755132</t>
+          <t>755294</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1397991</t>
+          <t>1397045</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1414725</t>
+          <t>1413377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1002-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1002-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2679</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6789</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1668</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>447</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4613</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4728</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,57%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2679</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6392</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>118701</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>114591</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>120730</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,41%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>104503</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>101558</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>105724</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>101443</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>105729</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,43%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,65%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,55%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>99,58%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>118701</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>114988</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>120723</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,79%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>337</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>219132</t>
+          <t>219300</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>225768</t>
+          <t>225705</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6940</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4008</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1756</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8359</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1411</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7979</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3002</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>866</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7459</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>250754</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>246816</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>253028</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,27%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>373</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>249197</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>244846</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>251449</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>245226</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>251794</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,42%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>250754</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>246297</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>252890</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>494222</t>
+          <t>494029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>503523</t>
+          <t>503430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4496</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3292</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>1167</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7234</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7148</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,58%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,67%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4039</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>140702</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>137019</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>124256</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>120314</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>120400</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>126381</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,42%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,33%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>94,4%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,09%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>140702</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>137476</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,15%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>397</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>260067</t>
+          <t>260472</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>267623</t>
+          <t>267654</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5394</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>616</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3506</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5934</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>204023</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>200655</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>205384</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>193481</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>190591</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>191009</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,19%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>204023</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>200115</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>205382</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>592</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>393515</t>
+          <t>393575</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>399467</t>
+          <t>399470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8521</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4177</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15357</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>9584</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5571</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15385</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>14993</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>8521</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4825</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>14763</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12396</t>
+          <t>12002</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25768</t>
+          <t>25622</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>714179</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>707343</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>718523</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,88%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1003</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>671437</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>665636</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>675450</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>666028</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>675822</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,59%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>714179</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>707937</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>717875</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1377953</t>
+          <t>1378099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1391325</t>
+          <t>1391719</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4130</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1752</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8512</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4929</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2366</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9450</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8884</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,37%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4130</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1411</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8753</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14597</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>140383</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>136001</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>142761</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,14%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>141352</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>136831</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>143915</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>137397</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>143944</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,63%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,54%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,38%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>140383</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>135760</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>143102</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,14%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276197</t>
+          <t>276322</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>286165</t>
+          <t>285814</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9496</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4939</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15841</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3745</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1419</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8884</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1485</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8483</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9496</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5058</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15352</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20763</t>
+          <t>20157</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>257605</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>251260</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>262162</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>230731</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>225592</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>233057</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>225993</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>232991</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,4%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>257605</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>251749</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>262043</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,44%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>480813</t>
+          <t>481419</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>493495</t>
+          <t>493416</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,74 +3356,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3310</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7173</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1438</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5068</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5065</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>3,27%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3310</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1297</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7337</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>10137</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>155261</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>151398</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>157279</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>153396</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>149766</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>149769</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,07%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>96,73%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>155261</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>151234</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>157274</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,91%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,37%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>441</t>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>304372</t>
+          <t>303268</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>311412</t>
+          <t>311365</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3704,102 +3704,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4761</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>665</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4040</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4599</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4972</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6171</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1617</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5261</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -3812,74 +3812,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>177006</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>173196</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>170672</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>167297</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>166738</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,61%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,32%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>177006</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>172985</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>503</t>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>344033</t>
+          <t>343123</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17887</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11363</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25718</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>10777</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6422</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17518</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6421</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>17680</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17887</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>11606</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>26197</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20506</t>
+          <t>21163</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37721</t>
+          <t>38840</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -4155,74 +4155,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>730255</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>722424</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>736779</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1002</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>696151</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>689410</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>700506</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>689248</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>700507</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,48%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,09%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1041</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>730255</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>721945</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>736536</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,61%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>96,5%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2043</t>
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1417349</t>
+          <t>1416230</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1434564</t>
+          <t>1433907</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2149</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10048</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1577</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>450</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4292</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4482</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,2%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5330</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2559</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9451</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11883</t>
+          <t>12332</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>118834</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>114116</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>122015</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,91%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>130077</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>127362</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>127172</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>131204</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,8%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,74%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,6%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>118834</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>114713</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>121605</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,71%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>92,39%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>387</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>243935</t>
+          <t>243486</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>252158</t>
+          <t>252267</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2620</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6475</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5366</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9982</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9757</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2620</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6536</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>255441</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>251586</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>257370</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>324</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>205151</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>200535</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>208511</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>200760</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>208149</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,45%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>255441</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>251525</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>257421</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,98%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>454532</t>
+          <t>454973</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>464177</t>
+          <t>464251</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,107 +5303,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4714</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1363</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4772</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4830</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4963</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -5416,74 +5416,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>187209</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>183858</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,28%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>187209</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>183800</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>533</t>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>372508</t>
+          <t>372641</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5651,102 +5651,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4090</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>772</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3913</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3212</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1536</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4207</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5389</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1536</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4650</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -5759,102 +5759,102 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>173284</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>169958</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>172529</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>169388</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>170089</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,55%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,15%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>173284</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>169841</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>345812</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>341959</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>347348</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>99,56%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>345812</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>342698</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>347348</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6040</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16584</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>7714</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4151</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13589</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3827</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>12962</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>10077</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6091</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>16307</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11636</t>
+          <t>12253</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25341</t>
+          <t>25723</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>734767</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>728260</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>738804</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1049</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>696657</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>690782</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>700220</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>691409</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>700544</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,9%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>734767</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>728537</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>738753</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1423874</t>
+          <t>1423492</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1437579</t>
+          <t>1436962</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,107 +6564,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1332</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4294</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4479</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>8,6%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4493</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1332</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4542</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>56179</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>53217</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>97,68%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>50783</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>47611</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>52090</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>91,4%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>61444</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>223</t>
@@ -6752,27 +6752,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>117623</t>
+          <t>101320</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114413</t>
+          <t>98134</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3987</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8864</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4569</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9279</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11413</t>
+          <t>9819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17541</t>
+          <t>14811</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>153535</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>148658</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>156221</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,47%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,37%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>154730</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>150020</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>157402</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,13%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>177607</t>
+          <t>141148</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>171141</t>
+          <t>135699</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>180750</t>
+          <t>143674</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>332337</t>
+          <t>294683</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>324312</t>
+          <t>288228</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>336701</t>
+          <t>298503</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1634</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5629</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2797</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>786</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7417</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1674</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>876</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9609</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>197539</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>193544</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>199173</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,17%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>170275</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>165655</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>172286</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>98,38%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,71%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>209813</t>
+          <t>171720</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>206401</t>
+          <t>167548</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>211487</t>
+          <t>173796</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>380088</t>
+          <t>369259</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>374951</t>
+          <t>364196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>382914</t>
+          <t>372133</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199173</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199173</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199173</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211487</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211487</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211487</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>384560</t>
+          <t>373845</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>384560</t>
+          <t>373845</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>384560</t>
+          <t>373845</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,107 +7593,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4255</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9635</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4034</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10508</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -7706,74 +7706,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>288390</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>283010</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>291684</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,55%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>342</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>275458</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>256553</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>301449</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>294975</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>304633</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>680</t>
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>576906</t>
+          <t>544943</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>570747</t>
+          <t>538535</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>580061</t>
+          <t>548294</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9876</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5041</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17203</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>8698</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5037</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15481</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19366</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,27 +8011,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12932</t>
+          <t>11820</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29264</t>
+          <t>27210</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>690001</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>682674</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>694836</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,59%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,28%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>656642</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>649859</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>660303</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,67%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>964</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>750313</t>
+          <t>620205</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>741603</t>
+          <t>613568</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>755294</t>
+          <t>624309</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,22 +8124,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1406955</t>
+          <t>1310206</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1397045</t>
+          <t>1301500</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1413377</t>
+          <t>1316890</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699877</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699877</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699877</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760969</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760969</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760969</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426309</t>
+          <t>1328710</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426309</t>
+          <t>1328710</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426309</t>
+          <t>1328710</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
